--- a/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -951,14 +951,14 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -987,7 +987,7 @@
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>-0.18249794</v>
+        <v>-0.15983657</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1134,14 +1134,14 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>-0.12966887</v>
+        <v>-0.20716736</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -1317,14 +1317,14 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -1353,7 +1353,7 @@
         </is>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>-0.01381177</v>
+        <v>0.08224580000000001</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1396,10 +1396,10 @@
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS5" t="n">
         <v>1</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1500,14 +1500,14 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1536,7 +1536,7 @@
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE6" t="n">
         <v>1</v>
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>0.08779118999999996</v>
+        <v>0.11513916</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="AK6" t="n">
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1719,7 +1719,7 @@
         </is>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
         <v>1</v>
@@ -1736,11 +1736,11 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>-0.23337663</v>
+        <v>-0.42282367</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.58</t>
         </is>
       </c>
       <c r="AK7" t="n">
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -1866,14 +1866,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1902,7 +1902,7 @@
         </is>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
         <v>1</v>
@@ -1919,24 +1919,24 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>-0.04596962</v>
+        <v>0.9740719999999999</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>+0.82</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="n">
         <v>0</v>
@@ -1963,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2049,14 +2049,14 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>1</v>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>-0.12028559</v>
+        <v>0.06217640999999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2232,14 +2232,14 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -2268,7 +2268,7 @@
         </is>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>1</v>
@@ -2285,21 +2285,21 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>0.01005472</v>
+        <v>-0.01958198</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -2311,7 +2311,7 @@
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2415,14 +2415,14 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -2451,7 +2451,7 @@
         </is>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -2468,21 +2468,21 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>0.005820259999999996</v>
+        <v>0.10554935</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -2491,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2598,14 +2598,14 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -2634,7 +2634,7 @@
         </is>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE12" t="n">
         <v>1</v>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>-0.21037133</v>
+        <v>-0.02464582</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2677,19 +2677,19 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AR12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV12" t="n">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2781,14 +2781,14 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
         <v>1</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="14">
@@ -2956,14 +2956,14 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -2995,10 +2995,10 @@
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG14" t="n">
         <v>1</v>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>0.09183689</v>
+        <v>-0.08492790000000001</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3044,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="BE14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BF14" t="n">
         <v>0</v>
@@ -3143,14 +3143,14 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -3182,10 +3182,10 @@
         <v>1</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG15" t="n">
         <v>1</v>
@@ -3196,21 +3196,21 @@
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>0.35511422</v>
+        <v>0.2837407200000001</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>+0.24</t>
+          <t>+0.13</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -3219,7 +3219,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3326,14 +3326,14 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -3365,10 +3365,10 @@
         <v>1</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG16" t="n">
         <v>1</v>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>0.25095129</v>
+        <v>0.20631808</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>+0.14</t>
+          <t>+0.05</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -3509,14 +3509,14 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -3548,10 +3548,10 @@
         <v>1</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG17" t="n">
         <v>1</v>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>0.06297892000000001</v>
+        <v>-0.16658368</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -3696,14 +3696,14 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -3735,10 +3735,10 @@
         <v>1</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG18" t="n">
         <v>1</v>
@@ -3749,21 +3749,21 @@
         </is>
       </c>
       <c r="AI18" t="n">
-        <v>0.07853840000000001</v>
+        <v>-0.02722645000000001</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
@@ -3778,16 +3778,16 @@
         <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS18" t="n">
         <v>2</v>
       </c>
       <c r="AT18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -3819,13 +3819,13 @@
         </is>
       </c>
       <c r="BE18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="BF18" t="n">
         <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
@@ -3883,14 +3883,14 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -3922,7 +3922,7 @@
         <v>1</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -3936,21 +3936,21 @@
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>0.37109027</v>
+        <v>0.30560348</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>+0.26</t>
+          <t>+0.15</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -3962,10 +3962,10 @@
         <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -3974,7 +3974,7 @@
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="BE19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BF19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG19" t="n">
         <v>1</v>
@@ -4070,14 +4070,14 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -4109,10 +4109,10 @@
         <v>1</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG20" t="n">
         <v>1</v>
@@ -4123,11 +4123,11 @@
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>1.54288407</v>
+        <v>1.36550291</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>+1.43</t>
+          <t>+1.21</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN20" t="n">
         <v>1</v>
@@ -4149,7 +4149,7 @@
         <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
         <v>0</v>
@@ -4192,7 +4192,7 @@
         <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4253,14 +4253,14 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -4292,7 +4292,7 @@
         <v>1</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -4306,11 +4306,11 @@
         </is>
       </c>
       <c r="AI21" t="n">
-        <v>0.05169223</v>
+        <v>0.06732060000000001</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AK21" t="n">
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -4479,10 +4479,10 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
-        <v>-0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG22" t="n">
         <v>1</v>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>0.4910534</v>
+        <v>0.38290769</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>+0.38</t>
+          <t>+0.23</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="BE22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BF22" t="n">
         <v>2</v>
@@ -4627,14 +4627,14 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -4666,7 +4666,7 @@
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>0.90786134</v>
+        <v>0.9326151499999999</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>+0.79</t>
+          <t>+0.78</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>

--- a/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -819,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -951,14 +951,14 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -990,10 +990,10 @@
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AG3" t="n">
         <v>1</v>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>-0.15983657</v>
+        <v>-0.33924476</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1134,14 +1134,14 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AG4" t="n">
         <v>1</v>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>-0.20716736</v>
+        <v>-0.27897634</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -1216,10 +1216,10 @@
         <v>1</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT4" t="n">
         <v>1</v>
@@ -1317,14 +1317,14 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="AG5" t="n">
         <v>1</v>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>0.08224580000000001</v>
+        <v>0.02069189000000001</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1500,14 +1500,14 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
         <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AG6" t="n">
         <v>1</v>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>0.11513916</v>
+        <v>-0.11025408</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.04</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1722,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="AG7" t="n">
         <v>1</v>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>-0.42282367</v>
+        <v>-0.31567238</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.58</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -1765,16 +1765,16 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="n">
         <v>2</v>
@@ -1866,14 +1866,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="AG8" t="n">
         <v>1</v>
@@ -1919,21 +1919,21 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>0.9740719999999999</v>
+        <v>1.1989092</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>+0.82</t>
+          <t>+0.85</t>
         </is>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
@@ -1951,16 +1951,16 @@
         <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -2049,14 +2049,14 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="AG9" t="n">
         <v>1</v>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>0.06217640999999999</v>
+        <v>-0.02793856000000003</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2128,10 +2128,10 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AR9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2232,14 +2232,14 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -2285,11 +2285,11 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>-0.01958198</v>
+        <v>0.007875009999999988</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -2299,7 +2299,7 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT10" t="n">
         <v>0</v>
@@ -2415,14 +2415,14 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2468,21 +2468,21 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>0.10554935</v>
+        <v>0.28123035</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -2491,7 +2491,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2500,7 +2500,7 @@
         <v>2</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2598,14 +2598,14 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -2637,10 +2637,10 @@
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="AG12" t="n">
         <v>1</v>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>-0.02464582</v>
+        <v>-0.05685378000000003</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2677,7 +2677,7 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR12" t="n">
         <v>3</v>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2781,14 +2781,14 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2956,14 +2956,14 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>-0.08492790000000001</v>
+        <v>0.3388528</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
         <v>3</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG14" t="n">
         <v>1</v>
@@ -3143,14 +3143,14 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3196,30 +3196,30 @@
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>0.2837407200000001</v>
+        <v>0.9038213400000001</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>+0.13</t>
+          <t>+0.56</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -3265,7 +3265,7 @@
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3326,14 +3326,14 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>0.20631808</v>
+        <v>0.33332638</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>+0.05</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -3509,14 +3509,14 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3562,21 +3562,21 @@
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>-0.16658368</v>
+        <v>-0.06395408999999999</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -3696,14 +3696,14 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3749,24 +3749,24 @@
         </is>
       </c>
       <c r="AI18" t="n">
-        <v>-0.02722645000000001</v>
+        <v>1.8970112</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>+1.55</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS18" t="n">
         <v>2</v>
@@ -3793,7 +3793,7 @@
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -3822,10 +3822,10 @@
         <v>6</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG18" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="19">
@@ -3883,14 +3883,14 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -3919,7 +3919,7 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
@@ -3936,21 +3936,21 @@
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>0.30560348</v>
+        <v>0.56133584</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>+0.21</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -3959,13 +3959,13 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
         <v>2</v>
       </c>
       <c r="AR19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS19" t="n">
         <v>0</v>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="BE19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF19" t="n">
         <v>3</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2</v>
       </c>
       <c r="BG19" t="n">
         <v>1</v>
@@ -4070,14 +4070,14 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -4123,21 +4123,21 @@
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>1.36550291</v>
+        <v>1.4725241</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>+1.21</t>
+          <t>+1.13</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN20" t="n">
         <v>1</v>
@@ -4253,14 +4253,14 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -4289,7 +4289,7 @@
         </is>
       </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE21" t="n">
         <v>1</v>
@@ -4306,11 +4306,11 @@
         </is>
       </c>
       <c r="AI21" t="n">
-        <v>0.06732060000000001</v>
+        <v>0.11707687</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK21" t="n">
@@ -4320,7 +4320,7 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4493,7 +4493,7 @@
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>0.38290769</v>
+        <v>0.57862116</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
@@ -4501,13 +4501,13 @@
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -4519,7 +4519,7 @@
         <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4566,7 +4566,7 @@
         <v>3</v>
       </c>
       <c r="BF22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
         <v>1</v>
@@ -4627,14 +4627,14 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4680,11 +4680,11 @@
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>0.9326151499999999</v>
+        <v>1.29106085</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>+0.78</t>
+          <t>+0.94</t>
         </is>
       </c>
       <c r="AK23" t="n">
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -4703,22 +4703,22 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AQ23" t="n">
         <v>1</v>
       </c>
       <c r="AR23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="BE23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG23" t="n">
         <v>4</v>

--- a/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -819,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -951,14 +951,14 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -990,62 +990,62 @@
         <v>1</v>
       </c>
       <c r="AE3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>S. Floranus</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.3249917500000001</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-0.80</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS3" t="n">
         <v>2</v>
       </c>
-      <c r="AF3" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>S. Floranus</t>
-        </is>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.33924476</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-0.69</t>
-        </is>
-      </c>
-      <c r="AK3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>37</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>1</v>
-      </c>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
@@ -1134,14 +1134,14 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -1173,50 +1173,50 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>D. Fonville</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>-0.4361394300000001</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AK4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR4" t="n">
         <v>2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>D. Fonville</t>
-        </is>
-      </c>
-      <c r="AI4" t="n">
-        <v>-0.27897634</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>-0.63</t>
-        </is>
-      </c>
-      <c r="AK4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>37</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1</v>
       </c>
       <c r="AS4" t="n">
         <v>1</v>
@@ -1317,14 +1317,14 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="AG5" t="n">
         <v>1</v>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>0.02069189000000001</v>
+        <v>-0.15133173</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1500,14 +1500,14 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1539,53 +1539,53 @@
         <v>1</v>
       </c>
       <c r="AE6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-0.6000000000000001</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>R. Bazoer</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.01603686000000015</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-0.49</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
         <v>2</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>R. Bazoer</t>
-        </is>
-      </c>
-      <c r="AI6" t="n">
-        <v>-0.11025408</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-0.46</t>
-        </is>
-      </c>
-      <c r="AK6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>37</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
@@ -1683,14 +1683,14 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1722,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.4</v>
+        <v>-0.6000000000000001</v>
       </c>
       <c r="AG7" t="n">
         <v>1</v>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>-0.31567238</v>
+        <v>-0.4972632900000001</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -1768,13 +1768,13 @@
         <v>3</v>
       </c>
       <c r="AS7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV7" t="n">
         <v>2</v>
@@ -1866,14 +1866,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1905,10 +1905,10 @@
         <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="AG8" t="n">
         <v>1</v>
@@ -1919,11 +1919,11 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>1.1989092</v>
+        <v>1.38313433</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>+0.85</t>
+          <t>+0.91</t>
         </is>
       </c>
       <c r="AK8" t="n">
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
@@ -1942,7 +1942,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -1951,7 +1951,7 @@
         <v>0</v>
       </c>
       <c r="AS8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
@@ -1960,7 +1960,7 @@
         <v>0</v>
       </c>
       <c r="AV8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2049,14 +2049,14 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
@@ -2088,10 +2088,10 @@
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="AG9" t="n">
         <v>1</v>
@@ -2102,21 +2102,21 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>-0.02793856000000003</v>
+        <v>0.03867426999999998</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR9" t="n">
         <v>3</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2232,14 +2232,14 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2247,7 +2247,7 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
@@ -2271,7 +2271,7 @@
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -2285,21 +2285,21 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>0.007875009999999988</v>
+        <v>0.003999769999999986</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -2415,14 +2415,14 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -2454,7 +2454,7 @@
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2468,21 +2468,21 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>0.28123035</v>
+        <v>0.54245359</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>+0.07</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -2500,19 +2500,19 @@
         <v>2</v>
       </c>
       <c r="AS11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV11" t="n">
         <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2598,14 +2598,14 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -2637,10 +2637,10 @@
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="AG12" t="n">
         <v>1</v>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>-0.05685378000000003</v>
+        <v>0.03604985999999996</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2677,22 +2677,22 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AR12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
         <v>3</v>
       </c>
-      <c r="AS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>2</v>
-      </c>
       <c r="AU12" t="n">
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2781,14 +2781,14 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE13" t="n">
         <v>1</v>
@@ -2836,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -2956,14 +2956,14 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -3009,21 +3009,21 @@
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>0.3388528</v>
+        <v>0.38640536</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3038,7 +3038,7 @@
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="BE14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BF14" t="n">
         <v>1</v>
@@ -3143,14 +3143,14 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         </is>
       </c>
       <c r="S15" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -3179,7 +3179,7 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
@@ -3196,11 +3196,11 @@
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>0.9038213400000001</v>
+        <v>1.09731771</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>+0.56</t>
+          <t>+0.63</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -3210,7 +3210,7 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -3326,14 +3326,14 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="S16" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -3362,7 +3362,7 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
@@ -3379,21 +3379,21 @@
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>0.33332638</v>
+        <v>0.53759313</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>+0.07</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
@@ -3509,14 +3509,14 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
       <c r="S17" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3562,11 +3562,11 @@
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>-0.06395408999999999</v>
+        <v>-0.03631828000000001</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN17" t="n">
         <v>0</v>
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
@@ -3696,14 +3696,14 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         </is>
       </c>
       <c r="S18" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE18" t="n">
         <v>1</v>
@@ -3749,11 +3749,11 @@
         </is>
       </c>
       <c r="AI18" t="n">
-        <v>1.8970112</v>
+        <v>2.13217661</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>+1.55</t>
+          <t>+1.66</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3763,7 +3763,7 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN18" t="n">
         <v>1</v>
@@ -3883,14 +3883,14 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -3898,7 +3898,7 @@
         </is>
       </c>
       <c r="S19" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -3919,50 +3919,50 @@
         </is>
       </c>
       <c r="AD19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>L. Sané</t>
+        </is>
+      </c>
+      <c r="AI19" t="n">
+        <v>0.62047724</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>+0.15</t>
+        </is>
+      </c>
+      <c r="AK19" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
         <v>2</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>L. Sané</t>
-        </is>
-      </c>
-      <c r="AI19" t="n">
-        <v>0.56133584</v>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>+0.21</t>
-        </is>
-      </c>
-      <c r="AK19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>37</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR19" t="n">
         <v>4</v>
@@ -4009,7 +4009,7 @@
         <v>5</v>
       </c>
       <c r="BF19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BG19" t="n">
         <v>1</v>
@@ -4070,14 +4070,14 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="S20" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -4106,7 +4106,7 @@
         </is>
       </c>
       <c r="AD20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE20" t="n">
         <v>1</v>
@@ -4123,11 +4123,11 @@
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>1.4725241</v>
+        <v>1.48650218</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>+1.13</t>
+          <t>+1.02</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4137,7 +4137,7 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN20" t="n">
         <v>1</v>
@@ -4161,7 +4161,7 @@
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
@@ -4253,14 +4253,14 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -4268,7 +4268,7 @@
         </is>
       </c>
       <c r="S21" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -4289,100 +4289,100 @@
         </is>
       </c>
       <c r="AD21" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>K. Havertz</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.05153332</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>+0.58</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>50</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="BE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF21" t="n">
         <v>2</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>K. Havertz</t>
-        </is>
-      </c>
-      <c r="AI21" t="n">
-        <v>0.11707687</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AK21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>37</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
-      <c r="BE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>0</v>
-      </c>
       <c r="BG21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -4440,14 +4440,14 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         </is>
       </c>
       <c r="S22" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4493,21 +4493,21 @@
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>0.57862116</v>
+        <v>0.8184201800000001</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>+0.23</t>
+          <t>+0.35</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
@@ -4519,7 +4519,7 @@
         <v>2</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
@@ -4563,10 +4563,10 @@
         </is>
       </c>
       <c r="BE22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BF22" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BG22" t="n">
         <v>1</v>
@@ -4627,14 +4627,14 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="S23" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -4663,7 +4663,7 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4680,11 +4680,11 @@
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>1.29106085</v>
+        <v>1.43717443</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>+0.94</t>
+          <t>+0.97</t>
         </is>
       </c>
       <c r="AK23" t="n">
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="AN23" t="n">
         <v>0</v>
@@ -4706,10 +4706,10 @@
         <v>2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>
@@ -4750,10 +4750,10 @@
         </is>
       </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BF23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BG23" t="n">
         <v>4</v>

--- a/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG23"/>
+  <dimension ref="A1:BG26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -819,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -951,14 +951,14 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -990,53 +990,53 @@
         <v>1</v>
       </c>
       <c r="AE3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>S. Floranus</t>
+        </is>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.88397993</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>-1.49</t>
+        </is>
+      </c>
+      <c r="AK3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS3" t="n">
         <v>3</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>-0.6000000000000001</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>S. Floranus</t>
-        </is>
-      </c>
-      <c r="AI3" t="n">
-        <v>-0.3249917500000001</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>-0.80</t>
-        </is>
-      </c>
-      <c r="AK3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>2</v>
       </c>
       <c r="AT3" t="n">
         <v>0</v>
@@ -1134,14 +1134,14 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF4" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AG4" t="n">
         <v>1</v>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>-0.4361394300000001</v>
+        <v>-0.7935819799999999</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.40</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -1216,16 +1216,16 @@
         <v>1</v>
       </c>
       <c r="AR4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
         <v>2</v>
       </c>
-      <c r="AS4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1</v>
-      </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -1317,14 +1317,14 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="AG5" t="n">
         <v>1</v>
@@ -1370,11 +1370,11 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>-0.15133173</v>
+        <v>0.0006645100000000018</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK5" t="n">
@@ -1384,7 +1384,7 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1399,19 +1399,19 @@
         <v>1</v>
       </c>
       <c r="AR5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" t="n">
         <v>2</v>
       </c>
-      <c r="AS5" t="n">
-        <v>1</v>
-      </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -1500,14 +1500,14 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1539,10 +1539,10 @@
         <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AG6" t="n">
         <v>1</v>
@@ -1553,21 +1553,21 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>-0.01603686000000015</v>
+        <v>-0.46341613</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
@@ -1683,14 +1683,14 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1722,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.6000000000000001</v>
+        <v>-1</v>
       </c>
       <c r="AG7" t="n">
         <v>1</v>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>-0.4972632900000001</v>
+        <v>-0.84031126</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="AR7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AS7" t="n">
         <v>2</v>
@@ -1777,7 +1777,7 @@
         <v>2</v>
       </c>
       <c r="AV7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW7" t="n">
         <v>0</v>
@@ -1866,14 +1866,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1905,56 +1905,56 @@
         <v>1</v>
       </c>
       <c r="AE8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>L. Comenencia</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.5849043</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>+0.98</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
         <v>3</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>L. Comenencia</t>
-        </is>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.38313433</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>+0.91</t>
-        </is>
-      </c>
-      <c r="AK8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>0</v>
       </c>
       <c r="AS8" t="n">
         <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2049,14 +2049,18 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>50</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
+        <v>68</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>LCF(2)</t>
+        </is>
+      </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2064,10 +2068,16 @@
         </is>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
-      </c>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>LCF(2)</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>23</v>
+      </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
@@ -2088,10 +2098,10 @@
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="AG9" t="n">
         <v>1</v>
@@ -2102,21 +2112,21 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>0.03867426999999998</v>
+        <v>-0.06045000000000003</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2218,10 +2228,12 @@
           <t>bbgnf53iva9u2rzc6xz045j9x</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="n">
+        <v>2</v>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -2232,14 +2244,18 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>50</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
+        <v>64</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>RCF(2)</t>
+        </is>
+      </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -2247,10 +2263,16 @@
         </is>
       </c>
       <c r="S10" t="n">
-        <v>50</v>
-      </c>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
+        <v>45</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>RCF(2)</t>
+        </is>
+      </c>
+      <c r="U10" t="n">
+        <v>19</v>
+      </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr"/>
@@ -2271,13 +2293,13 @@
         <v>1</v>
       </c>
       <c r="AE10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2285,21 +2307,21 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>0.003999769999999986</v>
+        <v>0.05179965</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
@@ -2401,10 +2423,12 @@
           <t>alfx6xxo38q6hmydbcr0rw67e</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="n">
+        <v>2</v>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -2415,14 +2439,14 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -2430,7 +2454,7 @@
         </is>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
@@ -2454,13 +2478,13 @@
         <v>1</v>
       </c>
       <c r="AE11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2468,21 +2492,21 @@
         </is>
       </c>
       <c r="AI11" t="n">
-        <v>0.54245359</v>
+        <v>0.5265733</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>+0.07</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
@@ -2598,14 +2622,14 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2613,7 +2637,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -2637,10 +2661,10 @@
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="AG12" t="n">
         <v>1</v>
@@ -2651,21 +2675,21 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>0.03604985999999996</v>
+        <v>-0.40957784</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2680,13 +2704,13 @@
         <v>6</v>
       </c>
       <c r="AR12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
         <v>5</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>3</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
@@ -2734,37 +2758,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+          <t>3csexoalt9hfesmo2p4619ga4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M. Neuer</t>
+          <t>J. Antonisse</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> 11</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>64pzn3jdqo6y2izlpm8n3tvpx</t>
+          <t>ix6hcbfujuw3mgefzpsnp2zu</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2773,30 +2797,34 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" t="n">
+        <v>45</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2</v>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N13" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Q13" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S13" t="n">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -2808,35 +2836,47 @@
       <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+          <t>3csexoalt9hfesmo2p4619ga4</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
         <v>3</v>
       </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>J. Antonisse</t>
+        </is>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.09012795999999998</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="AK13" t="n">
+        <v>14</v>
+      </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AM13" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2845,13 +2885,13 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
@@ -2863,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
         <v>0</v>
@@ -2886,19 +2926,15 @@
       <c r="BC13" t="n">
         <v>0</v>
       </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
+      <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2909,37 +2945,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+          <t>3csexoalt9hfesmo2p4619ga4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>J. Kimmich</t>
+          <t>J. Margaritha</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6</t>
+          <t xml:space="preserve"> 16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LCF(2)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>97nv3y9z2ajz6b4ynoo0jn3kl</t>
+          <t>6dpxvfpnaua6y4gevop02qc8a</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2948,30 +2984,34 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" t="n">
+        <v>64</v>
+      </c>
+      <c r="L14" t="n">
+        <v>2</v>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N14" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="Q14" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>LCF(2)</t>
         </is>
       </c>
       <c r="S14" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -2983,47 +3023,47 @@
       <c r="AA14" t="inlineStr"/>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+          <t>3csexoalt9hfesmo2p4619ga4</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>J. Kimmich</t>
+          <t>J. Margaritha</t>
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>0.38640536</v>
+        <v>0.01045677</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AM14" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3032,19 +3072,19 @@
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
         <v>0</v>
@@ -3073,19 +3113,15 @@
       <c r="BC14" t="n">
         <v>0</v>
       </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
+      <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -3101,17 +3137,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>N. Brown</t>
+          <t>M. Neuer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 18</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3121,12 +3157,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>cr4e64yry1ttwcjxh2klb4ui2</t>
+          <t>64pzn3jdqo6y2izlpm8n3tvpx</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -3143,22 +3179,22 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -3179,53 +3215,41 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>1</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>N. Brown</t>
-        </is>
-      </c>
-      <c r="AI15" t="n">
-        <v>1.09731771</v>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>+0.63</t>
-        </is>
-      </c>
-      <c r="AK15" t="n">
-        <v>5</v>
-      </c>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
       <c r="AL15" t="n">
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
@@ -3234,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -3260,15 +3284,19 @@
       <c r="BC15" t="n">
         <v>0</v>
       </c>
-      <c r="BD15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
       <c r="BF15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -3284,17 +3312,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A. Pavlović</t>
+          <t>J. Kimmich</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 5</t>
+          <t xml:space="preserve"> 6</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LCM(2)</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3304,12 +3332,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9u0jnvttp25l5bp2pvx7pces</t>
+          <t>97nv3y9z2ajz6b4ynoo0jn3kl</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -3326,22 +3354,22 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>LCM(2)</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -3362,59 +3390,59 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="AG16" t="n">
         <v>1</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>A. Pavlović</t>
+          <t>J. Kimmich</t>
         </is>
       </c>
       <c r="AI16" t="n">
-        <v>0.53759313</v>
+        <v>1.49485593</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>+0.07</t>
+          <t>+0.89</t>
         </is>
       </c>
       <c r="AK16" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
@@ -3443,15 +3471,19 @@
       <c r="BC16" t="n">
         <v>0</v>
       </c>
-      <c r="BD16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
@@ -3467,17 +3499,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>J. Tah</t>
+          <t>N. Brown</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4</t>
+          <t xml:space="preserve"> 18</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RCB(2)</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3487,12 +3519,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5ec2ede9uwbft3wby33mwowyd</t>
+          <t>cr4e64yry1ttwcjxh2klb4ui2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -3509,22 +3541,22 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>RCB(2)</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -3545,7 +3577,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3558,55 +3590,55 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>J. Tah</t>
+          <t>N. Brown</t>
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>-0.03631828000000001</v>
+        <v>1.94480759</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>+1.34</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
@@ -3626,19 +3658,15 @@
       <c r="BC17" t="n">
         <v>0</v>
       </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
+      <c r="BD17" t="inlineStr"/>
       <c r="BE17" t="n">
         <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BG17" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3654,17 +3682,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>N. Schlotterbeck</t>
+          <t>A. Pavlović</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15</t>
+          <t xml:space="preserve"> 5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LCB(2)</t>
+          <t>LCM(2)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3674,12 +3702,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>d5mck7rf48chzersephpx29d5</t>
+          <t>9u0jnvttp25l5bp2pvx7pces</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -3696,22 +3724,22 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>LCB(2)</t>
+          <t>LCM(2)</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -3732,68 +3760,68 @@
         </is>
       </c>
       <c r="AD18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>A. Pavlović</t>
+        </is>
+      </c>
+      <c r="AI18" t="n">
+        <v>0.83841814</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>+0.23</t>
+        </is>
+      </c>
+      <c r="AK18" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
         <v>3</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>N. Schlotterbeck</t>
-        </is>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.13217661</v>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>+1.66</t>
-        </is>
-      </c>
-      <c r="AK18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>4</v>
-      </c>
       <c r="AS18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -3813,19 +3841,15 @@
       <c r="BC18" t="n">
         <v>0</v>
       </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
+      <c r="BD18" t="inlineStr"/>
       <c r="BE18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG18" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3841,17 +3865,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>L. Sané</t>
+          <t>J. Tah</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 19</t>
+          <t xml:space="preserve"> 4</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RCB(2)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3861,12 +3885,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>4603xrdk721lqhd1ejn62x5n9</t>
+          <t>5ec2ede9uwbft3wby33mwowyd</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3883,22 +3907,22 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>RCB(2)</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -3919,38 +3943,38 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AG19" t="n">
         <v>1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>L. Sané</t>
+          <t>J. Tah</t>
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>0.62047724</v>
+        <v>0.29958196</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>+0.15</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -3959,22 +3983,22 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
         <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -4002,17 +4026,17 @@
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="BE19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BF19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BG19" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="20">
@@ -4028,17 +4052,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>F. Nmecha</t>
+          <t>N. Schlotterbeck</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23</t>
+          <t xml:space="preserve"> 15</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RCM(2)</t>
+          <t>LCB(2)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4048,12 +4072,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>6384gzzxuxs6pvmrn8qx4d7u1</t>
+          <t>d5mck7rf48chzersephpx29d5</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -4070,22 +4094,22 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>RCM(2)</t>
+          <t>LCB(2)</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -4106,59 +4130,59 @@
         </is>
       </c>
       <c r="AD20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>N. Schlotterbeck</t>
+        </is>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.18014703</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>+1.57</t>
+        </is>
+      </c>
+      <c r="AK20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT20" t="n">
         <v>3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>F. Nmecha</t>
-        </is>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.48650218</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>+1.02</t>
-        </is>
-      </c>
-      <c r="AK20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
       </c>
       <c r="AU20" t="n">
         <v>1</v>
@@ -4187,15 +4211,19 @@
       <c r="BC20" t="n">
         <v>0</v>
       </c>
-      <c r="BD20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BF20" t="n">
         <v>2</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21">
@@ -4211,17 +4239,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>K. Havertz</t>
+          <t>L. Sané</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 7</t>
+          <t xml:space="preserve"> 19</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4231,12 +4259,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>ed20ebhqi5c32vbbsze8r6yuh</t>
+          <t>4603xrdk721lqhd1ejn62x5n9</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -4253,22 +4281,22 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -4289,53 +4317,53 @@
         </is>
       </c>
       <c r="AD21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>L. Sané</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>0.87470136</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>+0.27</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ21" t="n">
         <v>3</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>K. Havertz</t>
-        </is>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.05153332</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>+0.58</t>
-        </is>
-      </c>
-      <c r="AK21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1</v>
-      </c>
       <c r="AR21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AS21" t="n">
         <v>0</v>
@@ -4344,13 +4372,13 @@
         <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -4376,13 +4404,13 @@
         </is>
       </c>
       <c r="BE21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BF21" t="n">
+        <v>5</v>
+      </c>
+      <c r="BG21" t="n">
         <v>2</v>
-      </c>
-      <c r="BG21" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -4398,17 +4426,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>J. Musiala</t>
+          <t>F. Nmecha</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10</t>
+          <t xml:space="preserve"> 23</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RCM(2)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4418,12 +4446,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>bhsdzppop8jwjsxwftizot1t6</t>
+          <t>6384gzzxuxs6pvmrn8qx4d7u1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -4440,22 +4468,22 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>RCM(2)</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -4476,7 +4504,7 @@
         </is>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4489,37 +4517,37 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>J. Musiala</t>
+          <t>F. Nmecha</t>
         </is>
       </c>
       <c r="AI22" t="n">
-        <v>0.8184201800000001</v>
+        <v>1.88741101</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>+0.35</t>
+          <t>+1.28</t>
         </is>
       </c>
       <c r="AK22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
         <v>2</v>
@@ -4531,13 +4559,13 @@
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
@@ -4557,19 +4585,15 @@
       <c r="BC22" t="n">
         <v>0</v>
       </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
+      <c r="BD22" t="inlineStr"/>
       <c r="BE22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BG22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -4585,17 +4609,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>F. Wirtz</t>
+          <t>K. Havertz</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 17</t>
+          <t xml:space="preserve"> 7</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4605,12 +4629,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2k5g68ywtr79lc45wozvifqlm</t>
+          <t>ed20ebhqi5c32vbbsze8r6yuh</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -4627,22 +4651,22 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -4663,100 +4687,663 @@
         </is>
       </c>
       <c r="AD23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>K. Havertz</t>
+        </is>
+      </c>
+      <c r="AI23" t="n">
+        <v>1.43641167</v>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>+0.83</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="BE23" t="n">
         <v>3</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH23" t="inlineStr">
+      <c r="BF23" t="n">
+        <v>2</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cjc09ujyfc1ks4blsyl8hbfv8</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>J. Musiala</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 10</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>bhsdzppop8jwjsxwftizot1t6</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>63</v>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>63</v>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="S24" t="n">
+        <v>63</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>J. Musiala</t>
+        </is>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.88656598</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>+1.28</t>
+        </is>
+      </c>
+      <c r="AK24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>63</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="BE24" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cjc09ujyfc1ks4blsyl8hbfv8</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>F. Wirtz</t>
         </is>
       </c>
-      <c r="AI23" t="n">
-        <v>1.43717443</v>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>+0.97</t>
-        </is>
-      </c>
-      <c r="AK23" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>50</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP23" t="n">
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 17</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2k5g68ywtr79lc45wozvifqlm</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>68</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>68</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>LW</t>
+        </is>
+      </c>
+      <c r="S25" t="n">
+        <v>68</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr"/>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>F. Wirtz</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.78513085</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>+1.18</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>2</v>
       </c>
-      <c r="AQ23" t="n">
+      <c r="AR25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="n">
         <v>2</v>
       </c>
-      <c r="AR23" t="n">
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="BE25" t="n">
+        <v>10</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG25" t="n">
         <v>5</v>
       </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU23" t="n">
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cjc09ujyfc1ks4blsyl8hbfv8</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>D. Undav</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 26</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>6rutvrgco8li4nyz7tfayxb6x</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>63</v>
+      </c>
+      <c r="L26" t="n">
         <v>2</v>
       </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="BE23" t="n">
-        <v>8</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>4</v>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>5</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>68</v>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>D. Undav</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
+        <v>0.63422431</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>+0.03</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>63</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="inlineStr"/>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG26"/>
+  <dimension ref="A1:BG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,14 +780,14 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="S2" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -819,7 +819,7 @@
         <v>1</v>
       </c>
       <c r="AE2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
@@ -951,14 +951,14 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
@@ -990,10 +990,10 @@
         <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF3" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="AG3" t="n">
         <v>1</v>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>-0.88397993</v>
+        <v>-1.19167856</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>-1.87</t>
         </is>
       </c>
       <c r="AK3" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
@@ -1134,14 +1134,14 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
@@ -1173,10 +1173,10 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="AG4" t="n">
         <v>1</v>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>-0.7935819799999999</v>
+        <v>-1.23510343</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.40</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AK4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN4" t="n">
         <v>0</v>
@@ -1213,13 +1213,13 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR4" t="n">
         <v>5</v>
       </c>
       <c r="AS4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT4" t="n">
         <v>2</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1317,14 +1317,14 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -1332,7 +1332,7 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
@@ -1356,10 +1356,10 @@
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="AG5" t="n">
         <v>1</v>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>0.0006645100000000018</v>
+        <v>-0.02161849999999998</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN5" t="n">
         <v>0</v>
@@ -1393,22 +1393,22 @@
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS5" t="n">
         <v>3</v>
       </c>
-      <c r="AS5" t="n">
-        <v>2</v>
-      </c>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
         <v>1</v>
@@ -1439,7 +1439,7 @@
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1500,14 +1500,14 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
@@ -1539,53 +1539,53 @@
         <v>1</v>
       </c>
       <c r="AE6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>R. Bazoer</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>-0.1186791300000003</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AK6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="n">
         <v>5</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>R. Bazoer</t>
-        </is>
-      </c>
-      <c r="AI6" t="n">
-        <v>-0.46341613</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
-      <c r="AK6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>68</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>2</v>
       </c>
       <c r="AT6" t="n">
         <v>1</v>
@@ -1683,14 +1683,14 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -1698,7 +1698,7 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
@@ -1722,10 +1722,10 @@
         <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF7" t="n">
-        <v>-1</v>
+        <v>-1.4</v>
       </c>
       <c r="AG7" t="n">
         <v>1</v>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>-0.84031126</v>
+        <v>-1.35394418</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>-2.03</t>
         </is>
       </c>
       <c r="AK7" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
         <v>0</v>
@@ -1762,16 +1762,16 @@
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR7" t="n">
         <v>5</v>
       </c>
       <c r="AS7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU7" t="n">
         <v>2</v>
@@ -1805,7 +1805,7 @@
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1866,14 +1866,14 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
@@ -1905,56 +1905,56 @@
         <v>1</v>
       </c>
       <c r="AE8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>L. Comenencia</t>
+        </is>
+      </c>
+      <c r="AI8" t="n">
+        <v>1.69255935</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>+1.02</t>
+        </is>
+      </c>
+      <c r="AK8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
         <v>5</v>
       </c>
-      <c r="AF8" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>L. Comenencia</t>
-        </is>
-      </c>
-      <c r="AI8" t="n">
-        <v>1.5849043</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>+0.98</t>
-        </is>
-      </c>
-      <c r="AK8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>68</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>3</v>
-      </c>
       <c r="AS8" t="n">
         <v>2</v>
       </c>
       <c r="AT8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU8" t="n">
         <v>0</v>
@@ -1988,7 +1988,7 @@
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG8" t="n">
         <v>0</v>
@@ -2035,10 +2035,12 @@
           <t>apzgvyoya5b4yd6vpev9o7krt</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -2049,7 +2051,7 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -2060,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -2076,7 +2078,7 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
@@ -2098,13 +2100,13 @@
         <v>1</v>
       </c>
       <c r="AE9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF9" t="n">
-        <v>-0.25</v>
+        <v>-0.3</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2112,21 +2114,21 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>-0.06045000000000003</v>
+        <v>0.2751438299999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AK9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
@@ -2138,10 +2140,10 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR9" t="n">
         <v>4</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -2181,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2307,15 +2309,15 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>0.05179965</v>
+        <v>0.05243757999999998</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2496,11 +2498,11 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AK11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2622,14 +2624,14 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -2637,7 +2639,7 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
@@ -2661,10 +2663,10 @@
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="AG12" t="n">
         <v>1</v>
@@ -2675,21 +2677,21 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>-0.40957784</v>
+        <v>-0.3699190399999999</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-1.04</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
@@ -2701,10 +2703,10 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AS12" t="n">
         <v>1</v>
@@ -2713,7 +2715,7 @@
         <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV12" t="n">
         <v>1</v>
@@ -2744,7 +2746,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2809,14 +2811,14 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>45</v>
       </c>
       <c r="Q13" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -2824,7 +2826,7 @@
         </is>
       </c>
       <c r="S13" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
@@ -2848,10 +2850,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="AG13" t="n">
         <v>2</v>
@@ -2862,21 +2864,21 @@
         </is>
       </c>
       <c r="AI13" t="n">
-        <v>0.09012795999999998</v>
+        <v>-0.04196373</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AK13" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
         <v>90</v>
       </c>
       <c r="AM13" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
@@ -2891,7 +2893,7 @@
         <v>1</v>
       </c>
       <c r="AR13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
@@ -2900,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -2996,14 +2998,14 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>64</v>
       </c>
       <c r="Q14" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -3011,7 +3013,7 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
@@ -3035,7 +3037,7 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -3049,21 +3051,21 @@
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>0.01045677</v>
+        <v>0.01403889999999999</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="AK14" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AL14" t="n">
         <v>64</v>
       </c>
       <c r="AM14" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
@@ -3075,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3118,7 +3120,7 @@
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3132,37 +3134,37 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+          <t>3csexoalt9hfesmo2p4619ga4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>M. Neuer</t>
+          <t>G. Kastaneer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve"> 19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>64pzn3jdqo6y2izlpm8n3tvpx</t>
+          <t>3a89nlkh1p3l3qi6o70uzp5ud</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -3171,30 +3173,34 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="n">
+        <v>82</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2</v>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="Q15" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>GK</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S15" t="n">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
@@ -3206,35 +3212,47 @@
       <c r="AA15" t="inlineStr"/>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+          <t>3csexoalt9hfesmo2p4619ga4</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Curaçao</t>
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>G. Kastaneer</t>
+        </is>
+      </c>
+      <c r="AI15" t="n">
+        <v>-0.07398321000000001</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>22</v>
+      </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>82</v>
       </c>
       <c r="AM15" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
@@ -3261,7 +3279,7 @@
         <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
         <v>0</v>
@@ -3284,11 +3302,7 @@
       <c r="BC15" t="n">
         <v>0</v>
       </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>GK</t>
-        </is>
-      </c>
+      <c r="BD15" t="inlineStr"/>
       <c r="BE15" t="n">
         <v>0</v>
       </c>
@@ -3296,7 +3310,7 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3312,17 +3326,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>J. Kimmich</t>
+          <t>M. Neuer</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3332,12 +3346,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>97nv3y9z2ajz6b4ynoo0jn3kl</t>
+          <t>64pzn3jdqo6y2izlpm8n3tvpx</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -3354,22 +3368,22 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>RB</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="S16" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
@@ -3390,65 +3404,53 @@
         </is>
       </c>
       <c r="AD16" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE16" t="n">
         <v>1</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
         <v>1</v>
       </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>J. Kimmich</t>
-        </is>
-      </c>
-      <c r="AI16" t="n">
-        <v>1.49485593</v>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>+0.89</t>
-        </is>
-      </c>
-      <c r="AK16" t="n">
-        <v>7</v>
-      </c>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
       <c r="AL16" t="n">
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
         <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW16" t="n">
         <v>0</v>
@@ -3473,17 +3475,17 @@
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>MID</t>
+          <t>GK</t>
         </is>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -3499,17 +3501,17 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>N. Brown</t>
+          <t>J. Kimmich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 18</t>
+          <t xml:space="preserve"> 6</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3519,18 +3521,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>cr4e64yry1ttwcjxh2klb4ui2</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>97nv3y9z2ajz6b4ynoo0jn3kl</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -3541,22 +3545,22 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>RB</t>
         </is>
       </c>
       <c r="S17" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
@@ -3577,7 +3581,7 @@
         </is>
       </c>
       <c r="AD17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3586,44 +3590,44 @@
         <v>-0.2</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>N. Brown</t>
+          <t>J. Kimmich</t>
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>1.94480759</v>
+        <v>2.27049837</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>+1.34</t>
+          <t>+1.60</t>
         </is>
       </c>
       <c r="AK17" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AS17" t="n">
         <v>0</v>
@@ -3632,13 +3636,13 @@
         <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
         <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
@@ -3658,15 +3662,19 @@
       <c r="BC17" t="n">
         <v>0</v>
       </c>
-      <c r="BD17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
@@ -3682,17 +3690,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A. Pavlović</t>
+          <t>N. Brown</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 5</t>
+          <t xml:space="preserve"> 18</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LCM(2)</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3702,18 +3710,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9u0jnvttp25l5bp2pvx7pces</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>cr4e64yry1ttwcjxh2klb4ui2</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -3724,22 +3734,22 @@
         </is>
       </c>
       <c r="N18" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>LCM(2)</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="S18" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
@@ -3766,62 +3776,62 @@
         <v>1</v>
       </c>
       <c r="AF18" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>A. Pavlović</t>
+          <t>N. Brown</t>
         </is>
       </c>
       <c r="AI18" t="n">
-        <v>0.83841814</v>
+        <v>1.94480759</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>+0.23</t>
+          <t>+1.27</t>
         </is>
       </c>
       <c r="AK18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AL18" t="n">
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AR18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX18" t="n">
         <v>0</v>
@@ -3846,7 +3856,7 @@
         <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -3865,17 +3875,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>J. Tah</t>
+          <t>A. Pavlović</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 4</t>
+          <t xml:space="preserve"> 5</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RCB(2)</t>
+          <t>LCM(2)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3885,12 +3895,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>5ec2ede9uwbft3wby33mwowyd</t>
+          <t>9u0jnvttp25l5bp2pvx7pces</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -3907,22 +3917,22 @@
         </is>
       </c>
       <c r="N19" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>RCB(2)</t>
+          <t>LCM(2)</t>
         </is>
       </c>
       <c r="S19" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
@@ -3943,38 +3953,38 @@
         </is>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE19" t="n">
         <v>1</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="AG19" t="n">
         <v>1</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>J. Tah</t>
+          <t>A. Pavlović</t>
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>0.29958196</v>
+        <v>1.09747182</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>+0.42</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
@@ -3989,16 +3999,16 @@
         <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AS19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV19" t="n">
         <v>0</v>
@@ -4024,19 +4034,15 @@
       <c r="BC19" t="n">
         <v>0</v>
       </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
+      <c r="BD19" t="inlineStr"/>
       <c r="BE19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
         <v>1</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -4052,17 +4058,17 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>N. Schlotterbeck</t>
+          <t>J. Tah</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 15</t>
+          <t xml:space="preserve"> 4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LCB(2)</t>
+          <t>RCB(2)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4072,18 +4078,20 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>d5mck7rf48chzersephpx29d5</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>5ec2ede9uwbft3wby33mwowyd</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -4094,22 +4102,22 @@
         </is>
       </c>
       <c r="N20" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>LCB(2)</t>
+          <t>RCB(2)</t>
         </is>
       </c>
       <c r="S20" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
@@ -4139,59 +4147,59 @@
         <v>-0.2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>N. Schlotterbeck</t>
+          <t>J. Tah</t>
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>2.18014703</v>
+        <v>0.29958196</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>+1.57</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="AK20" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AN20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ20" t="n">
         <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AS20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AT20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
         <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
         <v>0</v>
@@ -4217,13 +4225,13 @@
         </is>
       </c>
       <c r="BE20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BF20" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG20" t="n">
-        <v>7.5</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="21">
@@ -4239,17 +4247,17 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>L. Sané</t>
+          <t>N. Schlotterbeck</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 19</t>
+          <t xml:space="preserve"> 15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>LCB(2)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4259,12 +4267,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4603xrdk721lqhd1ejn62x5n9</t>
+          <t>d5mck7rf48chzersephpx29d5</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -4281,22 +4289,22 @@
         </is>
       </c>
       <c r="N21" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>LCB(2)</t>
         </is>
       </c>
       <c r="S21" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
@@ -4317,68 +4325,68 @@
         </is>
       </c>
       <c r="AD21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>N. Schlotterbeck</t>
+        </is>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.40920039</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>+1.73</t>
+        </is>
+      </c>
+      <c r="AK21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS21" t="n">
         <v>5</v>
       </c>
-      <c r="AE21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>L. Sané</t>
-        </is>
-      </c>
-      <c r="AI21" t="n">
-        <v>0.87470136</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>+0.27</t>
-        </is>
-      </c>
-      <c r="AK21" t="n">
-        <v>9</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>68</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ21" t="n">
+      <c r="AT21" t="n">
         <v>3</v>
       </c>
-      <c r="AR21" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
       <c r="AU21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV21" t="n">
         <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX21" t="n">
         <v>0</v>
@@ -4400,17 +4408,17 @@
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>FWD</t>
+          <t>DEF</t>
         </is>
       </c>
       <c r="BE21" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BF21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BG21" t="n">
-        <v>2</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="22">
@@ -4426,17 +4434,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>F. Nmecha</t>
+          <t>L. Sané</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 23</t>
+          <t xml:space="preserve"> 19</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RCM(2)</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4446,12 +4454,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6384gzzxuxs6pvmrn8qx4d7u1</t>
+          <t>4603xrdk721lqhd1ejn62x5n9</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -4468,22 +4476,22 @@
         </is>
       </c>
       <c r="N22" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>RCM(2)</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="S22" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
@@ -4504,54 +4512,54 @@
         </is>
       </c>
       <c r="AD22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>L. Sané</t>
+        </is>
+      </c>
+      <c r="AI22" t="n">
+        <v>0.9960812100000001</v>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>+0.32</t>
+        </is>
+      </c>
+      <c r="AK22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR22" t="n">
         <v>5</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>F. Nmecha</t>
-        </is>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.88741101</v>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>+1.28</t>
-        </is>
-      </c>
-      <c r="AK22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>68</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2</v>
-      </c>
       <c r="AS22" t="n">
         <v>0</v>
       </c>
@@ -4559,13 +4567,13 @@
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV22" t="n">
         <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
         <v>0</v>
@@ -4585,15 +4593,19 @@
       <c r="BC22" t="n">
         <v>0</v>
       </c>
-      <c r="BD22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BF22" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -4609,17 +4621,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>K. Havertz</t>
+          <t>F. Nmecha</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 7</t>
+          <t xml:space="preserve"> 23</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RCM(2)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4629,18 +4641,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>ed20ebhqi5c32vbbsze8r6yuh</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>6384gzzxuxs6pvmrn8qx4d7u1</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -4651,22 +4665,22 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>RCM(2)</t>
         </is>
       </c>
       <c r="S23" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="T23" t="inlineStr"/>
       <c r="U23" t="inlineStr"/>
@@ -4693,32 +4707,32 @@
         <v>1</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>K. Havertz</t>
+          <t>F. Nmecha</t>
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>1.43641167</v>
+        <v>1.88741101</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>+0.83</t>
+          <t>+1.21</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AN23" t="n">
         <v>1</v>
@@ -4730,25 +4744,25 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AS23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV23" t="n">
         <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AX23" t="n">
         <v>0</v>
@@ -4768,19 +4782,15 @@
       <c r="BC23" t="n">
         <v>0</v>
       </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>FWD</t>
-        </is>
-      </c>
+      <c r="BD23" t="inlineStr"/>
       <c r="BE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF23" t="n">
         <v>3</v>
       </c>
-      <c r="BF23" t="n">
-        <v>2</v>
-      </c>
       <c r="BG23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -4796,17 +4806,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>J. Musiala</t>
+          <t>K. Havertz</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10</t>
+          <t xml:space="preserve"> 7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4816,20 +4826,18 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>bhsdzppop8jwjsxwftizot1t6</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>2</v>
-      </c>
+          <t>ed20ebhqi5c32vbbsze8r6yuh</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -4840,22 +4848,22 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>CF</t>
         </is>
       </c>
       <c r="S24" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
@@ -4876,100 +4884,100 @@
         </is>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
       </c>
       <c r="AF24" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>J. Musiala</t>
+          <t>K. Havertz</t>
         </is>
       </c>
       <c r="AI24" t="n">
-        <v>1.88656598</v>
+        <v>2.52892411</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>+1.28</t>
+          <t>+1.85</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="AN24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AR24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="BE24" t="n">
         <v>3</v>
       </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD24" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="BE24" t="n">
-        <v>5</v>
-      </c>
       <c r="BF24" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="BG24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25">
@@ -4985,17 +4993,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>F. Wirtz</t>
+          <t>J. Musiala</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 17</t>
+          <t xml:space="preserve"> 10</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5005,18 +5013,20 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2k5g68ywtr79lc45wozvifqlm</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>bhsdzppop8jwjsxwftizot1t6</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -5027,22 +5037,22 @@
         </is>
       </c>
       <c r="N25" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>LW</t>
+          <t>AM</t>
         </is>
       </c>
       <c r="S25" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
@@ -5063,100 +5073,100 @@
         </is>
       </c>
       <c r="AD25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>J. Musiala</t>
+        </is>
+      </c>
+      <c r="AI25" t="n">
+        <v>1.90952472</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>+1.23</t>
+        </is>
+      </c>
+      <c r="AK25" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>63</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ25" t="n">
         <v>5</v>
       </c>
-      <c r="AE25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>F. Wirtz</t>
-        </is>
-      </c>
-      <c r="AI25" t="n">
-        <v>1.78513085</v>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>+1.18</t>
-        </is>
-      </c>
-      <c r="AK25" t="n">
+      <c r="AR25" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="BE25" t="n">
         <v>5</v>
       </c>
-      <c r="AL25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>68</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>4</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AR25" t="n">
+      <c r="BF25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG25" t="n">
         <v>7</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD25" t="inlineStr">
-        <is>
-          <t>MID</t>
-        </is>
-      </c>
-      <c r="BE25" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF25" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG25" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -5172,32 +5182,32 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>D. Undav</t>
+          <t>F. Wirtz</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 26</t>
+          <t xml:space="preserve"> 17</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6rutvrgco8li4nyz7tfayxb6x</t>
+          <t>2k5g68ywtr79lc45wozvifqlm</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -5206,34 +5216,30 @@
           <t>no</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>63</v>
-      </c>
-      <c r="L26" t="n">
-        <v>2</v>
-      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>LW</t>
         </is>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
@@ -5254,95 +5260,1046 @@
         </is>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>F. Wirtz</t>
+        </is>
+      </c>
+      <c r="AI26" t="n">
+        <v>1.84244256</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>+1.17</t>
+        </is>
+      </c>
+      <c r="AK26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="BE26" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cjc09ujyfc1ks4blsyl8hbfv8</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>A. Rüdiger</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RCB(2)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6fzbp94hf19ysotdassrqdc5x</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>72</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N27" t="n">
+        <v>23</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>95</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>RCB(2)</t>
+        </is>
+      </c>
+      <c r="S27" t="n">
+        <v>23</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
         <v>-0</v>
       </c>
-      <c r="AG26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH26" t="inlineStr">
+      <c r="AG27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>A. Rüdiger</t>
+        </is>
+      </c>
+      <c r="AI27" t="n">
+        <v>-0.11643003</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AK27" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>72</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="BE27" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cjc09ujyfc1ks4blsyl8hbfv8</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>W. Anton</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 3</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3uqn1adw8rarez1gpen9vng7p</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>82</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>13</v>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>82</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>95</v>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="S28" t="n">
+        <v>13</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>W. Anton</t>
+        </is>
+      </c>
+      <c r="AI28" t="n">
+        <v>0.15832289</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>-0.52</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>82</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="inlineStr"/>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cjc09ujyfc1ks4blsyl8hbfv8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>L. Goretzka</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 8</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RCM(2)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>4w4ldzomkj7fhrc51iimz8no5</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>72</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N29" t="n">
+        <v>23</v>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>95</v>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>RCM(2)</t>
+        </is>
+      </c>
+      <c r="S29" t="n">
+        <v>23</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AD29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>L. Goretzka</t>
+        </is>
+      </c>
+      <c r="AI29" t="n">
+        <v>0.38760098</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>-0.29</t>
+        </is>
+      </c>
+      <c r="AK29" t="n">
+        <v>14</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>72</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="BE29" t="n">
+        <v>3</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cjc09ujyfc1ks4blsyl8hbfv8</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>D. Raum</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 22</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2uz1cmslnjjzsgfcgji26kqg9</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>72</v>
+      </c>
+      <c r="L30" t="n">
+        <v>2</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N30" t="n">
+        <v>23</v>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>95</v>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>LB</t>
+        </is>
+      </c>
+      <c r="S30" t="n">
+        <v>23</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AD30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>D. Raum</t>
+        </is>
+      </c>
+      <c r="AI30" t="n">
+        <v>0.57234332</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>-0.10</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>12</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>72</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="BE30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cjc09ujyfc1ks4blsyl8hbfv8</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>D. Undav</t>
         </is>
       </c>
-      <c r="AI26" t="n">
-        <v>0.63422431</v>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>+0.03</t>
-        </is>
-      </c>
-      <c r="AK26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AL26" t="n">
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 26</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>6rutvrgco8li4nyz7tfayxb6x</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
         <v>63</v>
       </c>
-      <c r="AM26" t="n">
-        <v>68</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="inlineStr"/>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG26" t="n">
+      <c r="L31" t="n">
+        <v>2</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>32</v>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>63</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>95</v>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>AM</t>
+        </is>
+      </c>
+      <c r="S31" t="n">
+        <v>32</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>3l2t2db0c5ow2f7s7bhr6mij4</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="AD31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>D. Undav</t>
+        </is>
+      </c>
+      <c r="AI31" t="n">
+        <v>2.38441905</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>+1.71</t>
+        </is>
+      </c>
+      <c r="AK31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>63</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>95</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="inlineStr"/>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG31" t="n">
         <v>0</v>
       </c>
     </row>

--- a/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
@@ -1008,7 +1008,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>-1.86</t>
         </is>
       </c>
       <c r="AK3" t="n">
@@ -1187,11 +1187,11 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>-1.23510343</v>
+        <v>-1.33510343</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-2.00</t>
         </is>
       </c>
       <c r="AK4" t="n">
@@ -1213,7 +1213,7 @@
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR4" t="n">
         <v>5</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1370,11 +1370,11 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>-0.02161849999999998</v>
+        <v>-0.02009665999999998</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="AK5" t="n">
@@ -1553,11 +1553,11 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>-0.1186791300000003</v>
+        <v>-0.2267301500000003</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AK6" t="n">
@@ -1582,7 +1582,7 @@
         <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AS6" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.03</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="AK7" t="n">
@@ -1919,11 +1919,11 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>1.69255935</v>
+        <v>1.69103751</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>+1.02</t>
+          <t>+1.03</t>
         </is>
       </c>
       <c r="AK8" t="n">
@@ -2114,11 +2114,11 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>0.2751438299999999</v>
+        <v>0.1751438299999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="AK9" t="n">
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR9" t="n">
         <v>4</v>
@@ -2183,7 +2183,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2313,7 +2313,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AK11" t="n">
@@ -2681,7 +2681,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.04</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="AK12" t="n">
@@ -2864,11 +2864,11 @@
         </is>
       </c>
       <c r="AI13" t="n">
-        <v>-0.04196373</v>
+        <v>-0.06518450000000001</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -3051,11 +3051,11 @@
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>0.01403889999999999</v>
+        <v>0.01830771999999997</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -3238,11 +3238,11 @@
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>-0.07398321000000001</v>
+        <v>-0.09298799000000001</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>+1.60</t>
+          <t>+1.61</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>+1.27</t>
+          <t>+1.28</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3970,7 +3970,7 @@
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>1.09747182</v>
+        <v>1.08279489</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4342,15 +4342,15 @@
         </is>
       </c>
       <c r="AI21" t="n">
-        <v>2.40920039</v>
+        <v>2.53489522</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>+1.73</t>
+          <t>+1.87</t>
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4368,7 +4368,7 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR21" t="n">
         <v>8</v>
@@ -4415,7 +4415,7 @@
         <v>10</v>
       </c>
       <c r="BF21" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BG21" t="n">
         <v>9.5</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>+0.32</t>
+          <t>+0.33</t>
         </is>
       </c>
       <c r="AK22" t="n">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>+1.21</t>
+          <t>+1.22</t>
         </is>
       </c>
       <c r="AK23" t="n">
@@ -4905,11 +4905,11 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>+1.85</t>
+          <t>+1.87</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5094,7 +5094,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>+1.23</t>
+          <t>+1.25</t>
         </is>
       </c>
       <c r="AK25" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>+1.17</t>
+          <t>+1.18</t>
         </is>
       </c>
       <c r="AK26" t="n">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -5659,11 +5659,11 @@
         </is>
       </c>
       <c r="AI28" t="n">
-        <v>0.15832289</v>
+        <v>0.11588031</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AK28" t="n">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-0.29</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -6041,7 +6041,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AK30" t="n">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="AI31" t="n">
-        <v>2.38441905</v>
+        <v>2.37227186</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
@@ -6257,7 +6257,7 @@
         <v>2</v>
       </c>
       <c r="AR31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS31" t="n">
         <v>0</v>

--- a/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
+++ b/bnc-streamlit-app/data/points/cjc09ujyfc1ks4blsyl8hbfv8_playerlog.xlsx
@@ -953,7 +953,11 @@
       <c r="N3" t="n">
         <v>95</v>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>RWB</t>
+        </is>
+      </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
@@ -966,10 +970,16 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>95</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
+        <v>72.7</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>RWB</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
+        <v>22.3</v>
+      </c>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr"/>
@@ -1004,11 +1014,11 @@
         </is>
       </c>
       <c r="AI3" t="n">
-        <v>-1.19167856</v>
+        <v>-1.17953137</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>-1.81</t>
         </is>
       </c>
       <c r="AK3" t="n">
@@ -1136,7 +1146,11 @@
       <c r="N4" t="n">
         <v>95</v>
       </c>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>LWB</t>
+        </is>
+      </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
@@ -1149,10 +1163,16 @@
         </is>
       </c>
       <c r="S4" t="n">
-        <v>95</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
+        <v>72.7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>LWB</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
+        <v>22.3</v>
+      </c>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
       <c r="X4" t="inlineStr"/>
@@ -1187,11 +1207,11 @@
         </is>
       </c>
       <c r="AI4" t="n">
-        <v>-1.33510343</v>
+        <v>-1.32659689</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-2.00</t>
+          <t>-1.96</t>
         </is>
       </c>
       <c r="AK4" t="n">
@@ -1319,7 +1339,11 @@
       <c r="N5" t="n">
         <v>95</v>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>RCB(3)</t>
+        </is>
+      </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
@@ -1332,10 +1356,16 @@
         </is>
       </c>
       <c r="S5" t="n">
-        <v>95</v>
-      </c>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
+        <v>72.7</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>RCB(3)</t>
+        </is>
+      </c>
+      <c r="U5" t="n">
+        <v>22.3</v>
+      </c>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
@@ -1370,15 +1400,15 @@
         </is>
       </c>
       <c r="AI5" t="n">
-        <v>-0.02009665999999998</v>
+        <v>-0.82364803</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.68</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="AK5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1502,7 +1532,11 @@
       <c r="N6" t="n">
         <v>95</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>CB(3)</t>
+        </is>
+      </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
@@ -1515,10 +1549,16 @@
         </is>
       </c>
       <c r="S6" t="n">
-        <v>95</v>
-      </c>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
+        <v>72.7</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>CB(3)</t>
+        </is>
+      </c>
+      <c r="U6" t="n">
+        <v>22.3</v>
+      </c>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
@@ -1553,15 +1593,15 @@
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>-0.2267301500000003</v>
+        <v>-0.2264945600000001</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="AK6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1685,7 +1725,11 @@
       <c r="N7" t="n">
         <v>95</v>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>LCB(3)</t>
+        </is>
+      </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
@@ -1698,10 +1742,16 @@
         </is>
       </c>
       <c r="S7" t="n">
-        <v>95</v>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
+        <v>72.7</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>LCB(3)</t>
+        </is>
+      </c>
+      <c r="U7" t="n">
+        <v>22.3</v>
+      </c>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
@@ -1736,11 +1786,11 @@
         </is>
       </c>
       <c r="AI7" t="n">
-        <v>-1.35394418</v>
+        <v>-1.3545334</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-2.02</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="AK7" t="n">
@@ -1868,7 +1918,11 @@
       <c r="N8" t="n">
         <v>95</v>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>RDM(2)</t>
+        </is>
+      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
@@ -1881,10 +1935,16 @@
         </is>
       </c>
       <c r="S8" t="n">
-        <v>95</v>
-      </c>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
+        <v>72.7</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>RDM(2)</t>
+        </is>
+      </c>
+      <c r="U8" t="n">
+        <v>22.3</v>
+      </c>
       <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
@@ -1919,11 +1979,11 @@
         </is>
       </c>
       <c r="AI8" t="n">
-        <v>1.69103751</v>
+        <v>1.69230026</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>+1.03</t>
+          <t>+1.06</t>
         </is>
       </c>
       <c r="AK8" t="n">
@@ -2055,7 +2115,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>LCF(2)</t>
+          <t>LCF(2), RCF(2)</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2078,10 +2138,16 @@
         </is>
       </c>
       <c r="U9" t="n">
-        <v>37</v>
-      </c>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
+        <v>27.7</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>RCF(2)</t>
+        </is>
+      </c>
+      <c r="W9" t="n">
+        <v>9.300000000000001</v>
+      </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
@@ -2114,11 +2180,11 @@
         </is>
       </c>
       <c r="AI9" t="n">
-        <v>0.1751438299999999</v>
+        <v>0.2304489099999999</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="AK9" t="n">
@@ -2140,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR9" t="n">
         <v>4</v>
@@ -2183,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2309,15 +2375,15 @@
         </is>
       </c>
       <c r="AI10" t="n">
-        <v>0.05243757999999998</v>
+        <v>-0.004850020000000024</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="AK10" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2335,7 +2401,7 @@
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -2378,7 +2444,7 @@
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG10" t="n">
         <v>0</v>
@@ -2498,7 +2564,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AK11" t="n">
@@ -2626,7 +2692,11 @@
       <c r="N12" t="n">
         <v>95</v>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>LDM(2)</t>
+        </is>
+      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
@@ -2639,10 +2709,16 @@
         </is>
       </c>
       <c r="S12" t="n">
-        <v>95</v>
-      </c>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
+        <v>72.7</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>LDM(2)</t>
+        </is>
+      </c>
+      <c r="U12" t="n">
+        <v>22.3</v>
+      </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
@@ -2677,15 +2753,15 @@
         </is>
       </c>
       <c r="AI12" t="n">
-        <v>-0.3699190399999999</v>
+        <v>-0.4504379799999998</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="AK12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2703,7 +2779,7 @@
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AR12" t="n">
         <v>9</v>
@@ -2746,7 +2822,7 @@
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="BG12" t="n">
         <v>0</v>
@@ -2864,15 +2940,15 @@
         </is>
       </c>
       <c r="AI13" t="n">
-        <v>-0.06518450000000001</v>
+        <v>0.1487633</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AL13" t="n">
         <v>90</v>
@@ -3000,7 +3076,11 @@
       <c r="N14" t="n">
         <v>31</v>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>RCF(2)</t>
+        </is>
+      </c>
       <c r="P14" t="n">
         <v>64</v>
       </c>
@@ -3013,10 +3093,16 @@
         </is>
       </c>
       <c r="S14" t="n">
-        <v>31</v>
-      </c>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
+        <v>8.699999999999999</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>RCF(2)</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
+        <v>22.3</v>
+      </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
@@ -3051,11 +3137,11 @@
         </is>
       </c>
       <c r="AI14" t="n">
-        <v>0.01830771999999997</v>
+        <v>0.01387809999999998</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.62</t>
         </is>
       </c>
       <c r="AK14" t="n">
@@ -3238,15 +3324,15 @@
         </is>
       </c>
       <c r="AI15" t="n">
-        <v>-0.09298799000000001</v>
+        <v>-0.08240395</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
         <v>82</v>
@@ -3598,11 +3684,11 @@
         </is>
       </c>
       <c r="AI17" t="n">
-        <v>2.27049837</v>
+        <v>2.16742319</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>+1.61</t>
+          <t>+1.54</t>
         </is>
       </c>
       <c r="AK17" t="n">
@@ -3791,7 +3877,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>+1.28</t>
+          <t>+1.31</t>
         </is>
       </c>
       <c r="AK18" t="n">
@@ -3970,11 +4056,11 @@
         </is>
       </c>
       <c r="AI19" t="n">
-        <v>1.08279489</v>
+        <v>1.14706044</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>+0.42</t>
+          <t>+0.51</t>
         </is>
       </c>
       <c r="AK19" t="n">
@@ -3996,7 +4082,7 @@
         <v>1</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR19" t="n">
         <v>6</v>
@@ -4039,7 +4125,7 @@
         <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4155,11 +4241,11 @@
         </is>
       </c>
       <c r="AI20" t="n">
-        <v>0.29958196</v>
+        <v>0.2995819599999999</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="AK20" t="n">
@@ -4342,15 +4428,15 @@
         </is>
       </c>
       <c r="AI21" t="n">
-        <v>2.53489522</v>
+        <v>2.44787056</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>+1.87</t>
+          <t>+1.82</t>
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -4368,17 +4454,17 @@
         <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR21" t="n">
         <v>8</v>
       </c>
       <c r="AS21" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT21" t="n">
         <v>5</v>
       </c>
-      <c r="AT21" t="n">
-        <v>3</v>
-      </c>
       <c r="AU21" t="n">
         <v>2</v>
       </c>
@@ -4412,10 +4498,10 @@
         </is>
       </c>
       <c r="BE21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BG21" t="n">
         <v>9.5</v>
@@ -4533,7 +4619,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>+0.33</t>
+          <t>+0.36</t>
         </is>
       </c>
       <c r="AK22" t="n">
@@ -4718,15 +4804,15 @@
         </is>
       </c>
       <c r="AI23" t="n">
-        <v>1.88741101</v>
+        <v>1.8341597</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>+1.22</t>
+          <t>+1.20</t>
         </is>
       </c>
       <c r="AK23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>0</v>
@@ -4744,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR23" t="n">
         <v>2</v>
@@ -4787,7 +4873,7 @@
         <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -4901,15 +4987,15 @@
         </is>
       </c>
       <c r="AI24" t="n">
-        <v>2.52892411</v>
+        <v>2.55289891</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>+1.87</t>
+          <t>+1.92</t>
         </is>
       </c>
       <c r="AK24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL24" t="n">
         <v>0</v>
@@ -5090,15 +5176,15 @@
         </is>
       </c>
       <c r="AI25" t="n">
-        <v>1.90952472</v>
+        <v>1.89450486</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>+1.25</t>
+          <t>+1.26</t>
         </is>
       </c>
       <c r="AK25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -5277,15 +5363,15 @@
         </is>
       </c>
       <c r="AI26" t="n">
-        <v>1.84244256</v>
+        <v>1.90174064</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>+1.18</t>
+          <t>+1.27</t>
         </is>
       </c>
       <c r="AK26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL26" t="n">
         <v>0</v>
@@ -5468,15 +5554,15 @@
         </is>
       </c>
       <c r="AI27" t="n">
-        <v>-0.11643003</v>
+        <v>-0.11508208</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>72</v>
@@ -5659,15 +5745,15 @@
         </is>
       </c>
       <c r="AI28" t="n">
-        <v>0.11588031</v>
+        <v>0.11033321</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AK28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL28" t="n">
         <v>82</v>
@@ -5846,11 +5932,11 @@
         </is>
       </c>
       <c r="AI29" t="n">
-        <v>0.38760098</v>
+        <v>0.37473967</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -6041,7 +6127,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AK30" t="n">
@@ -6228,7 +6314,7 @@
         </is>
       </c>
       <c r="AI31" t="n">
-        <v>2.37227186</v>
+        <v>2.34121197</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
